--- a/游戏设计王/骰宝数学-SicBo计算模型.xlsx
+++ b/游戏设计王/骰宝数学-SicBo计算模型.xlsx
@@ -280,11 +280,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -951,7 +952,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -970,6 +971,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1812,7 +1815,7 @@
       <c r="E4" s="4">
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="str">
+      <c r="F4" s="18" t="str">
         <f t="shared" ref="F4:F21" si="1">IF($E4=0,"",$E4/$C$23)</f>
         <v/>
       </c>
@@ -1821,7 +1824,7 @@
         <v/>
       </c>
       <c r="H4" s="4"/>
-      <c r="I4" s="5" t="str">
+      <c r="I4" s="18" t="str">
         <f t="shared" ref="I4:I21" si="3">IF(OR($E4=0,$H4=""),"",$F4*($H4+1))</f>
         <v/>
       </c>
@@ -1858,7 +1861,7 @@
         <f>SUM(D$4:D4)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="str">
+      <c r="F5" s="18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -1867,7 +1870,7 @@
         <v/>
       </c>
       <c r="H5" s="4"/>
-      <c r="I5" s="5" t="str">
+      <c r="I5" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1902,7 +1905,7 @@
         <f>SUM(D$4:D5)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="18">
         <f t="shared" si="1"/>
         <v>0.00462962962962963</v>
       </c>
@@ -1911,7 +1914,7 @@
         <v>216</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="5" t="str">
+      <c r="I6" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -1942,7 +1945,7 @@
         <f>SUM(D$4:D6)</f>
         <v>3</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="18">
         <f t="shared" si="1"/>
         <v>0.0138888888888889</v>
       </c>
@@ -1953,7 +1956,7 @@
       <c r="H7" s="7">
         <v>60</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="18">
         <f t="shared" si="3"/>
         <v>0.847222222222222</v>
       </c>
@@ -1987,7 +1990,7 @@
         <f>SUM(D$4:D7)</f>
         <v>6</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="18">
         <f t="shared" si="1"/>
         <v>0.0277777777777778</v>
       </c>
@@ -1998,7 +2001,7 @@
       <c r="H8" s="7">
         <v>20</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="18">
         <f t="shared" si="3"/>
         <v>0.583333333333333</v>
       </c>
@@ -2033,7 +2036,7 @@
         <f>SUM(D$4:D8)</f>
         <v>10</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="18">
         <f t="shared" si="1"/>
         <v>0.0462962962962963</v>
       </c>
@@ -2044,7 +2047,7 @@
       <c r="H9" s="7">
         <v>18</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="18">
         <f t="shared" si="3"/>
         <v>0.87962962962963</v>
       </c>
@@ -2075,7 +2078,7 @@
         <f>SUM(D$4:D9)</f>
         <v>15</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="18">
         <f t="shared" si="1"/>
         <v>0.0694444444444444</v>
       </c>
@@ -2086,7 +2089,7 @@
       <c r="H10" s="7">
         <v>12</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="18">
         <f t="shared" si="3"/>
         <v>0.902777777777778</v>
       </c>
@@ -2122,7 +2125,7 @@
         <f t="shared" ref="E11:E21" si="6">SUM(D5:D10)</f>
         <v>21</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="18">
         <f t="shared" si="1"/>
         <v>0.0972222222222222</v>
       </c>
@@ -2133,7 +2136,7 @@
       <c r="H11" s="7">
         <v>8</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="18">
         <f t="shared" si="3"/>
         <v>0.875</v>
       </c>
@@ -2169,7 +2172,7 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="18">
         <f t="shared" si="1"/>
         <v>0.115740740740741</v>
       </c>
@@ -2180,7 +2183,7 @@
       <c r="H12" s="7">
         <v>6</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="18">
         <f t="shared" si="3"/>
         <v>0.810185185185185</v>
       </c>
@@ -2211,7 +2214,7 @@
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="18">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
@@ -2222,7 +2225,7 @@
       <c r="H13" s="7">
         <v>6</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="18">
         <f t="shared" si="3"/>
         <v>0.875</v>
       </c>
@@ -2253,7 +2256,7 @@
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="18">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
@@ -2264,7 +2267,7 @@
       <c r="H14" s="7">
         <v>6</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="18">
         <f t="shared" si="3"/>
         <v>0.875</v>
       </c>
@@ -2295,7 +2298,7 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="18">
         <f t="shared" si="1"/>
         <v>0.115740740740741</v>
       </c>
@@ -2306,7 +2309,7 @@
       <c r="H15" s="7">
         <v>6</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="18">
         <f t="shared" si="3"/>
         <v>0.810185185185185</v>
       </c>
@@ -2337,7 +2340,7 @@
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="18">
         <f t="shared" si="1"/>
         <v>0.0972222222222222</v>
       </c>
@@ -2348,7 +2351,7 @@
       <c r="H16" s="7">
         <v>8</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="18">
         <f t="shared" si="3"/>
         <v>0.875</v>
       </c>
@@ -2379,7 +2382,7 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="18">
         <f t="shared" si="1"/>
         <v>0.0694444444444444</v>
       </c>
@@ -2390,7 +2393,7 @@
       <c r="H17" s="7">
         <v>12</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="18">
         <f t="shared" si="3"/>
         <v>0.902777777777778</v>
       </c>
@@ -2421,7 +2424,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="18">
         <f t="shared" si="1"/>
         <v>0.0462962962962963</v>
       </c>
@@ -2432,7 +2435,7 @@
       <c r="H18" s="7">
         <v>18</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="18">
         <f t="shared" si="3"/>
         <v>0.87962962962963</v>
       </c>
@@ -2463,7 +2466,7 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="18">
         <f t="shared" si="1"/>
         <v>0.0277777777777778</v>
       </c>
@@ -2474,7 +2477,7 @@
       <c r="H19" s="7">
         <v>20</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="18">
         <f t="shared" si="3"/>
         <v>0.583333333333333</v>
       </c>
@@ -2505,7 +2508,7 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="18">
         <f t="shared" si="1"/>
         <v>0.0138888888888889</v>
       </c>
@@ -2516,7 +2519,7 @@
       <c r="H20" s="7">
         <v>60</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="18">
         <f t="shared" si="3"/>
         <v>0.847222222222222</v>
       </c>
@@ -2547,7 +2550,7 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="18">
         <f t="shared" si="1"/>
         <v>0.00462962962962963</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>216</v>
       </c>
       <c r="H21" s="4"/>
-      <c r="I21" s="5" t="str">
+      <c r="I21" s="18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -2741,7 +2744,7 @@
         <f>25*3</f>
         <v>75</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="18">
         <f>$C27/$C$23</f>
         <v>0.347222222222222</v>
       </c>
@@ -2752,7 +2755,7 @@
       <c r="F27" s="7">
         <v>1</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="18">
         <f>$D27*($F27+1)</f>
         <v>0.694444444444444</v>
       </c>
@@ -2785,7 +2788,7 @@
         <f>5*3</f>
         <v>15</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="18">
         <f>$C28/$C$23</f>
         <v>0.0694444444444444</v>
       </c>
@@ -2796,7 +2799,7 @@
       <c r="F28" s="7">
         <v>2</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="18">
         <f>$D28*($F28+1)</f>
         <v>0.208333333333333</v>
       </c>
@@ -2826,7 +2829,7 @@
       <c r="C29" s="4">
         <v>1</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="18">
         <f>$C29/$C$23</f>
         <v>0.00462962962962963</v>
       </c>
@@ -2837,7 +2840,7 @@
       <c r="F29" s="7">
         <v>3</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="18">
         <f>$D29*($F29+1)</f>
         <v>0.0185185185185185</v>
       </c>
@@ -2873,7 +2876,7 @@
       <c r="F30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="19">
         <f>SUM($G$27:$G$29)</f>
         <v>0.921296296296296</v>
       </c>
@@ -3000,7 +3003,7 @@
         <f>SUMIF($B$4:$B$21,"&gt;=11",$E$4:$E$21)-SUMIF($B$4:$B$21,"&gt;=11",$J$4:$J$21)</f>
         <v>105</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="18">
         <f t="shared" ref="D34:D40" si="7">$C34/$C$23</f>
         <v>0.486111111111111</v>
       </c>
@@ -3011,7 +3014,7 @@
       <c r="F34" s="7">
         <v>1</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="18">
         <f t="shared" ref="G34:G39" si="9">$D34*($F34+1)</f>
         <v>0.972222222222222</v>
       </c>
@@ -3046,7 +3049,7 @@
         <f>SUMIF($B$4:$B$21,"&lt;=10",$E$4:$E$21)-SUMIF($B$4:$B$21,"&lt;=10",$J$4:$J$21)</f>
         <v>105</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="18">
         <f t="shared" si="7"/>
         <v>0.486111111111111</v>
       </c>
@@ -3057,7 +3060,7 @@
       <c r="F35" s="7">
         <v>1</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="18">
         <f t="shared" si="9"/>
         <v>0.972222222222222</v>
       </c>
@@ -3090,7 +3093,7 @@
         <f>4*6+3+3</f>
         <v>30</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="18">
         <f t="shared" si="7"/>
         <v>0.138888888888889</v>
       </c>
@@ -3101,7 +3104,7 @@
       <c r="F36" s="7">
         <v>5</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="18">
         <f t="shared" si="9"/>
         <v>0.833333333333333</v>
       </c>
@@ -3135,7 +3138,7 @@
         <f>5*3+1</f>
         <v>16</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="18">
         <f t="shared" si="7"/>
         <v>0.0740740740740741</v>
       </c>
@@ -3146,7 +3149,7 @@
       <c r="F37" s="7">
         <v>10</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="18">
         <f t="shared" si="9"/>
         <v>0.814814814814815</v>
       </c>
@@ -3174,7 +3177,7 @@
       <c r="C38" s="4">
         <v>1</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="18">
         <f t="shared" si="7"/>
         <v>0.00462962962962963</v>
       </c>
@@ -3185,7 +3188,7 @@
       <c r="F38" s="7">
         <v>180</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="18">
         <f t="shared" si="9"/>
         <v>0.837962962962963</v>
       </c>
@@ -3213,7 +3216,7 @@
         <f>SUM($J$4:$J$21)</f>
         <v>6</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="18">
         <f t="shared" si="7"/>
         <v>0.0277777777777778</v>
       </c>
@@ -3224,7 +3227,7 @@
       <c r="F39" s="7">
         <v>30</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="18">
         <f t="shared" si="9"/>
         <v>0.861111111111111</v>
       </c>
@@ -3254,7 +3257,7 @@
         <f>SUM($C$27:$C$29)</f>
         <v>91</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="18">
         <f t="shared" si="7"/>
         <v>0.421296296296296</v>
       </c>
@@ -3265,7 +3268,7 @@
       <c r="F40" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="18">
         <f>$G$30</f>
         <v>0.921296296296296</v>
       </c>
@@ -3386,7 +3389,7 @@
       <c r="C44" s="7">
         <v>1</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="18">
         <f>$D$34*(C44+1)</f>
         <v>0.972222222222222</v>
       </c>
@@ -3429,7 +3432,7 @@
       <c r="C45" s="7">
         <v>0.95</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="18">
         <f>$D$34*(C45+1)</f>
         <v>0.947916666666667</v>
       </c>
@@ -3465,7 +3468,7 @@
       <c r="C46" s="7">
         <v>24</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="18">
         <f>$D$39*(C46+1)</f>
         <v>0.694444444444444</v>
       </c>
@@ -3501,7 +3504,7 @@
       <c r="C47" s="7">
         <v>30</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="18">
         <f>$D$39*(C47+1)</f>
         <v>0.861111111111111</v>
       </c>
@@ -3542,7 +3545,7 @@
       <c r="C48" s="7">
         <v>31</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="18">
         <f>$D$39*(C48+1)</f>
         <v>0.888888888888889</v>
       </c>
@@ -3578,7 +3581,7 @@
       <c r="C49" s="7">
         <v>32</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="18">
         <f>$D$39*(C49+1)</f>
         <v>0.916666666666667</v>
       </c>
@@ -3614,7 +3617,7 @@
       <c r="C50" s="7">
         <v>33</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="18">
         <f>$D$39*(C50+1)</f>
         <v>0.944444444444444</v>
       </c>
